--- a/local/templates/schedule/MultiPlatformWithAgeGroups.xlsx
+++ b/local/templates/schedule/MultiPlatformWithAgeGroups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/templates/schedule/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/67.4.3+test/local/templates/schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0381B6A-DD9A-A548-AE17-BDEFBD19A1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF276350-6EA7-9843-ABC5-981D6CC63060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="3460" windowWidth="33340" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="1960" windowWidth="33020" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,17 @@
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
           </rPr>
-          <t>owlcms:fixMerges(4, [1, 2])</t>
+          <t xml:space="preserve">owlcms:mergeDown(4, 1, 2)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+          </rPr>
+          <t>owlcms:verticalBorders(4, 1, 11)</t>
         </r>
       </text>
     </comment>
@@ -742,11 +752,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1100,19 +1110,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1"/>
@@ -1128,10 +1138,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="2"/>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="7"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
